--- a/.planning/delay-detective-wbs.xlsx
+++ b/.planning/delay-detective-wbs.xlsx
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1746,13 +1746,13 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -1798,13 +1798,13 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -1850,13 +1850,13 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -1902,13 +1902,13 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr"/>
       <c r="K63" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr"/>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -3990,14 +3990,14 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr"/>
       <c r="K64" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -4042,14 +4042,14 @@
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr"/>
       <c r="K65" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>미시작</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -4094,14 +4094,14 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr"/>
       <c r="K66" s="23" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="L4" s="30" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행중(일부완료)</t>
         </is>
       </c>
     </row>
